--- a/public/templates/Template Upload Open FKR Pemusnahan.xlsx
+++ b/public/templates/Template Upload Open FKR Pemusnahan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dokumen Loginusa\Dokumen Loginusa\Template Project EIS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loginusa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D58CFB19-E5D1-4F3E-8BDC-52D2EFC1AD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE526C5A-5EDD-4895-AEFA-470768967DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{4A74284D-DADD-48E3-9BB5-E98CAE9B30CB}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{4A74284D-DADD-48E3-9BB5-E98CAE9B30CB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA4ECC9-5B24-42AF-9E78-04BAF6078D3C}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
@@ -439,79 +439,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>6000866</v>
+        <v>1000094</v>
       </c>
       <c r="B2" s="3">
-        <v>45785</v>
+        <v>46296</v>
       </c>
       <c r="C2" s="3">
-        <v>45788</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>6000867</v>
+        <v>6000686</v>
       </c>
       <c r="B3" s="3">
-        <v>45785</v>
+        <v>46296</v>
       </c>
       <c r="C3" s="3">
-        <v>45788</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>6000811</v>
-      </c>
-      <c r="B4" s="3">
-        <v>45785</v>
-      </c>
-      <c r="C4" s="3">
-        <v>45788</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>6000812</v>
-      </c>
-      <c r="B5" s="3">
-        <v>45785</v>
-      </c>
-      <c r="C5" s="3">
-        <v>45788</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>6000813</v>
-      </c>
-      <c r="B6" s="3">
-        <v>45785</v>
-      </c>
-      <c r="C6" s="3">
-        <v>45788</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6000814</v>
-      </c>
-      <c r="B7" s="3">
-        <v>45785</v>
-      </c>
-      <c r="C7" s="3">
-        <v>45788</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>6000819</v>
-      </c>
-      <c r="B8" s="3">
-        <v>45785</v>
-      </c>
-      <c r="C8" s="3">
-        <v>45788</v>
+        <v>46297</v>
       </c>
     </row>
   </sheetData>
